--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/WEST_VIRGINIA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/WEST_VIRGINIA_2014.xlsx
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C44">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C104">
